--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115840</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136115893</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136116126</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136116145</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136116279</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136116032</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115840</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136115893</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136116126</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136116145</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136116279</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136116032</v>
       </c>
       <c r="B11" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115840</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136115893</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136116126</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136116145</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136116279</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136116032</v>
       </c>
       <c r="B11" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78813</v>
+        <v>78819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115840</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136115893</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136116126</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136116145</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136116279</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136116032</v>
       </c>
       <c r="B11" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78819</v>
+        <v>78832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136115840</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>136115893</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136116126</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>136116145</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>136116279</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136116032</v>
       </c>
       <c r="B11" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25737-2026 artfynd.xlsx
+++ b/artfynd/A 25737-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136115801</v>
       </c>
       <c r="B2" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136116464</v>
       </c>
       <c r="B3" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136116376</v>
       </c>
       <c r="B4" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136116511</v>
       </c>
       <c r="B5" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136116460</v>
       </c>
       <c r="B12" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>136116508</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
